--- a/summer_camps/003_summer_camp_parental_release_medical_information_code_of_conduct--summer_camps.xlsx
+++ b/summer_camps/003_summer_camp_parental_release_medical_information_code_of_conduct--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'medical_condition_1',_'label':_'does_the_student_have_a_medical_condition_that_requires_medication?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>does_the_student_have_a_medical_condition_that_requires_medication?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'medical_condition_1', 'label': 'Does the student have a medical condition that requires medication?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Does the student have a medical condition that requires medication?</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'medical_condition_2',_'label':_'if_yes,_please_describe_the_condition.',_'type':_'text',_'options':_[]}</t>
+          <t>if_yes,_please_describe_the_condition.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'medical_condition_2', 'label': 'If Yes, please describe the condition.', 'type': 'text', 'options': []}</t>
+          <t>If Yes, please describe the condition.</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'medical_condition_3',_'label':_'has_the_student_ever_been_treated_in_a_hospital?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_been_treated_in_a_hospital?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'medical_condition_3', 'label': 'Has the student ever been treated in a hospital?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever been treated in a hospital?</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'medical_condition_4',_'label':_'has_the_student_ever_had_any_allergies?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_allergies?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'medical_condition_4', 'label': 'Has the student ever had any allergies?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any allergies?</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'medical_condition_5',_'label':_'has_the_student_ever_been_prescribed_any_medication?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_been_prescribed_any_medication?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'medical_condition_5', 'label': 'Has the student ever been prescribed any medication?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever been prescribed any medication?</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'medical_condition_6',_'label':_'has_the_student_ever_had_any_medical_tests_or_examinations?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_medical_tests_or_examinations?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'medical_condition_6', 'label': 'Has the student ever had any medical tests or examinations?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any medical tests or examinations?</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'medical_condition_7',_'label':_'has_the_student_ever_had_any_surgeries?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_surgeries?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'medical_condition_7', 'label': 'Has the student ever had any surgeries?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any surgeries?</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'medical_condition_8',_'label':_'has_the_student_ever_had_any_medical_conditions_that_may_affect_their_physical_ability_to_participate_in_camp_activities?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_medical_conditions_that_may_affect_their_physical_ability_to_participate_in_camp_activities?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'medical_condition_8', 'label': 'Has the student ever had any medical conditions that may affect their physical ability to participate in camp activities?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any medical conditions that may affect their physical ability to participate in camp activities?</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'medical_condition_9',_'label':_'has_the_student_ever_had_any_allergies_or_medical_conditions_that_may_impact_the_ability_of_any_camp_staff_to_care_for_the_student?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_allergies_or_medical_conditions_that_may_impact_the_ability_of_any_camp_staff_to_care_for_the_student?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'medical_condition_9', 'label': 'Has the student ever had any allergies or medical conditions that may impact the ability of any camp staff to care for the student?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any allergies or medical conditions that may impact the ability of any camp staff to care for the student?</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'medical_condition_10',_'label':_'has_the_student_ever_had_any_medical_conditions_that_may_impact_their_ability_to_participate_in_camp_activities?',_'type':_'select_one',_'options':_[{'id':_1,_'label':_true},_{'id':_2,_'label':_false}]}</t>
+          <t>has_the_student_ever_had_any_medical_conditions_that_may_impact_their_ability_to_participate_in_camp_activities?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'medical_condition_10', 'label': 'Has the student ever had any medical conditions that may impact their ability to participate in camp activities?', 'type': 'select_one', 'options': [{'id': 1, 'label': True}, {'id': 2, 'label': False}]}</t>
+          <t>Has the student ever had any medical conditions that may impact their ability to participate in camp activities?</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'terms_and_conditions',_'label':_'terms_and_conditions',_'type':_'text',_'options':_[]}</t>
+          <t>terms_and_conditions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'terms_and_conditions', 'label': 'Terms and Conditions', 'type': 'text', 'options': []}</t>
+          <t>Terms and Conditions</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
